--- a/dist/schedule.xlsx
+++ b/dist/schedule.xlsx
@@ -9,18 +9,17 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="181029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="等线"/>
       <charset val="134"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
@@ -28,23 +27,7 @@
     <font>
       <name val="等线"/>
       <charset val="134"/>
-      <family val="2"/>
       <sz val="9"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="SimSun"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <family val="3"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -74,9 +57,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -196,7 +177,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -229,26 +210,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -281,23 +245,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -460,11 +407,6 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -476,6 +418,9 @@
   </sheetPr>
   <dimension ref="A1:J400"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.8203125" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.17578125" customWidth="1" style="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -483,331 +428,356 @@
           <t>周一</t>
         </is>
       </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="C1" s="0" t="inlineStr">
         <is>
           <t>周二</t>
         </is>
       </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="E1" s="0" t="inlineStr">
         <is>
           <t>周三</t>
         </is>
       </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="G1" s="0" t="inlineStr">
         <is>
           <t>周四</t>
         </is>
       </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I1" s="0" t="inlineStr">
         <is>
           <t>周五</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>/</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">数学早读 </t>
+          <t>课程</t>
         </is>
       </c>
       <c r="C2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="D2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文早读 </t>
+          <t>课程</t>
         </is>
       </c>
       <c r="E2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="F2" s="0" t="inlineStr">
         <is>
-          <t>英语早读</t>
+          <t>课程</t>
         </is>
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
         <is>
-          <t>语文早读</t>
+          <t>课程</t>
         </is>
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t>7:00-7:30</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="J2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">英语早读 </t>
+          <t>课程</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理 </t>
+          <t xml:space="preserve">数学早读 </t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文 </t>
+          <t xml:space="preserve">语文早读 </t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">物理 </t>
+          <t>英语早读</t>
         </is>
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
         <is>
-          <t>数学</t>
+          <t>语文早读</t>
         </is>
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>8:00-8:40</t>
+          <t>7:00-7:30</t>
         </is>
       </c>
       <c r="J3" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">英语 </t>
+          <t xml:space="preserve">英语早读 </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t>8:50-9:30</t>
+          <t>8:00-8:40</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">体育 </t>
+          <t xml:space="preserve">物理 </t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>8:50-9:30</t>
+          <t>8:00-8:40</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">历史 </t>
+          <t xml:space="preserve">语文 </t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>8:50-9:30</t>
+          <t>8:00-8:40</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>数学</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>8:00-8:40</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">英语 </t>
-        </is>
-      </c>
-      <c r="G4" s="0" t="inlineStr">
-        <is>
-          <t>8:50-9:30</t>
-        </is>
-      </c>
-      <c r="H4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">数学 </t>
-        </is>
-      </c>
-      <c r="I4" s="0" t="inlineStr">
-        <is>
-          <t>8:50-9:30</t>
-        </is>
-      </c>
-      <c r="J4" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">体育 </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="inlineStr">
         <is>
-          <t>9:40-10:20</t>
+          <t>8:50-9:30</t>
         </is>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文 </t>
+          <t xml:space="preserve">体育 </t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>9:40-10:20</t>
+          <t>8:50-9:30</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">历史 </t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>8:50-9:30</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">英语 </t>
         </is>
       </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>9:40-10:20</t>
-        </is>
-      </c>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">历史 </t>
-        </is>
-      </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t>9:40-10:20</t>
+          <t>8:50-9:30</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文 </t>
+          <t xml:space="preserve">数学 </t>
         </is>
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t>9:40-10:20</t>
+          <t>8:50-9:30</t>
         </is>
       </c>
       <c r="J5" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">生物 </t>
+          <t xml:space="preserve">体育 </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">化学 </t>
+          <t xml:space="preserve">语文 </t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">心理 </t>
+          <t xml:space="preserve">英语 </t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">艺术 </t>
+          <t xml:space="preserve">历史 </t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">信息 </t>
+          <t xml:space="preserve">语文 </t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t>10:35-11:15</t>
+          <t>9:40-10:20</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">选修 </t>
+          <t xml:space="preserve">生物 </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">数学 </t>
+          <t xml:space="preserve">化学 </t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">地理 </t>
+          <t xml:space="preserve">心理 </t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">数学 </t>
+          <t xml:space="preserve">艺术 </t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">化学 </t>
+          <t xml:space="preserve">信息 </t>
         </is>
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>11:25-12:05</t>
+          <t>10:35-11:15</t>
         </is>
       </c>
       <c r="J7" s="0" t="inlineStr">
@@ -819,318 +789,617 @@
     <row r="8">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t>13:35-14:15</t>
+          <t>11:25-12:05</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">信息 </t>
+          <t xml:space="preserve">数学 </t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>13:35-14:15</t>
+          <t>11:25-12:05</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">地理 </t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>11:25-12:05</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">数学 </t>
         </is>
       </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>13:35-14:15</t>
-        </is>
-      </c>
-      <c r="F8" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">语文 </t>
-        </is>
-      </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>13:35-14:15</t>
+          <t>11:25-12:05</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">英语 </t>
+          <t xml:space="preserve">化学 </t>
         </is>
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t>13:00-13:40</t>
+          <t>11:25-12:05</t>
         </is>
       </c>
       <c r="J8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">数学 </t>
+          <t xml:space="preserve">选修 </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="inlineStr">
         <is>
-          <t>14:30-15:10</t>
+          <t>13:10-13:30</t>
         </is>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">生物 </t>
+          <t>午休</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>14:30-15:10</t>
+          <t>13:10-13:30</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">化学 </t>
+          <t>午休</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>14:30-15:10</t>
+          <t>13:10-13:30</t>
         </is>
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">地理 </t>
+          <t>午休</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>14:30-15:10</t>
+          <t>13:10-13:30</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">强基 </t>
+          <t>午休</t>
         </is>
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>13:55-14:35</t>
+          <t>12:40-13:00</t>
         </is>
       </c>
       <c r="J9" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">语文 </t>
+          <t>午休</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t>15:25-16:05</t>
+          <t>13:35-14:15</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
+          <t xml:space="preserve">信息 </t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">数学 </t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>13:35-14:15</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
           <t xml:space="preserve">英语 </t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>15:25-16:05</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">体育专项 </t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
-        <is>
-          <t>15:25-16:05</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">政治 </t>
-        </is>
-      </c>
-      <c r="G10" s="0" t="inlineStr">
-        <is>
-          <t>15:25-16:05</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">物理 </t>
-        </is>
-      </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>14:50-15:30</t>
+          <t>13:00-13:40</t>
         </is>
       </c>
       <c r="J10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">政治 </t>
+          <t xml:space="preserve">数学 </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="inlineStr">
         <is>
-          <t>16:15-16:55</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">班会 </t>
+          <t xml:space="preserve">生物 </t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>16:15-16:55</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="D11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">体育专项 </t>
+          <t xml:space="preserve">化学 </t>
         </is>
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>16:15-16:55</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">社团 </t>
+          <t xml:space="preserve">地理 </t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>16:15-16:55</t>
+          <t>14:30-15:10</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>紫竹讲坛\习读</t>
+          <t xml:space="preserve">强基 </t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="inlineStr">
+        <is>
+          <t>13:55-14:35</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">语文 </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="inlineStr">
         <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">英语 </t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育专项 </t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">政治 </t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>15:25-16:05</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">物理 </t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr">
+        <is>
+          <t>14:50-15:30</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">政治 </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">班会 </t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">体育专项 </t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">社团 </t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>16:15-16:55</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>紫竹讲坛\习读</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
           <t>18:00-19:00</t>
         </is>
       </c>
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">英语限时 </t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>18:00-19:00</t>
         </is>
       </c>
-      <c r="D12" s="0" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">物化限时 </t>
         </is>
       </c>
-      <c r="E12" s="0" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>18:00-19:00</t>
         </is>
       </c>
-      <c r="F12" s="0" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">语文限时 </t>
         </is>
       </c>
-      <c r="G12" s="0" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>18:00-19:00</t>
         </is>
       </c>
-      <c r="H12" s="0" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t xml:space="preserve">数学限时 </t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="D14" s="1" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>程子曦</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>END_C</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>康立轩</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>陈奕浩</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>倪宥霖</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>叶宇乐</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>上午擦黑板</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>孙丞怿</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>黄思源</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>李玥呈</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>张一铭</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>下午擦黑板</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>沈俊奕</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>font_size</t>
         </is>
       </c>
-      <c r="B20" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="inlineStr">
+      <c r="B30" s="0" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>window_width</t>
         </is>
       </c>
-      <c r="B21" s="0" t="n">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="inlineStr">
+      <c r="B31" s="0" t="n">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>window_height</t>
         </is>
       </c>
-      <c r="B22" s="0" t="n">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="inlineStr">
+      <c r="B32" s="0" t="n">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>excel_path</t>
         </is>
       </c>
-      <c r="B23" s="0" t="inlineStr">
-        <is>
-          <t>D:\tools\ClassroomListener\dist\schedule.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>D:\tools\ClassroomListener\schedule.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>col_width_0</t>
         </is>
       </c>
-      <c r="B24" s="0" t="n">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="inlineStr">
+      <c r="B34" s="0" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>col_width_1</t>
         </is>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B35" s="0" t="n">
         <v>190</v>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36"/>
     <row r="37"/>
     <row r="38"/>
